--- a/erp-server/erp-server-wms/src/main/resources/excel/sampleBorrowInfoTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/sampleBorrowInfoTemplate.xlsx
@@ -875,11 +875,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1410,52 +1413,52 @@
   <dimension ref="A1:L1"/>
   <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="19.725" customWidth="1"/>
-    <col min="2" max="3" width="20.0916666666667" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="7" width="17.8166666666667" customWidth="1"/>
-    <col min="8" max="8" width="17.725" customWidth="1"/>
-    <col min="9" max="10" width="15.5416666666667" customWidth="1"/>
-    <col min="11" max="11" width="17.8166666666667" customWidth="1"/>
-    <col min="12" max="12" width="19.725" customWidth="1"/>
+    <col min="1" max="1" width="19.725" style="1" customWidth="1"/>
+    <col min="2" max="3" width="20.0916666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="1" customWidth="1"/>
+    <col min="6" max="7" width="17.8166666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.725" style="1" customWidth="1"/>
+    <col min="9" max="10" width="15.5416666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.8166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.725" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
